--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.75055</v>
+        <v>16.98061</v>
       </c>
       <c r="D2" t="n">
-        <v>16.21599</v>
+        <v>16.56744</v>
       </c>
       <c r="E2" t="n">
-        <v>16.61033</v>
+        <v>16.76312</v>
       </c>
       <c r="F2" t="n">
-        <v>42.74211</v>
+        <v>44.52955</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05218</v>
+        <v>0.04892</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82713</v>
+        <v>1.81526</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.76072</v>
+        <v>16.9406</v>
       </c>
       <c r="D3" t="n">
-        <v>16.26375</v>
+        <v>16.33469</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70698</v>
+        <v>16.76295</v>
       </c>
       <c r="F3" t="n">
-        <v>41.76212</v>
+        <v>42.64647</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0514</v>
+        <v>0.05123</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84012</v>
+        <v>1.80946</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.74975</v>
+        <v>16.53636</v>
       </c>
       <c r="D4" t="n">
-        <v>16.46187</v>
+        <v>16.43449</v>
       </c>
       <c r="E4" t="n">
-        <v>16.7959</v>
+        <v>16.52778</v>
       </c>
       <c r="F4" t="n">
-        <v>42.4915</v>
+        <v>42.91696</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05082</v>
+        <v>0.05016</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82283</v>
+        <v>1.77905</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.74879</v>
+        <v>16.87413</v>
       </c>
       <c r="D6" t="n">
-        <v>16.10717</v>
+        <v>15.95562</v>
       </c>
       <c r="E6" t="n">
-        <v>16.30096</v>
+        <v>16.34377</v>
       </c>
       <c r="F6" t="n">
-        <v>21.63681</v>
+        <v>21.90431</v>
       </c>
       <c r="G6" t="n">
-        <v>33.76464</v>
+        <v>33.87373</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.81428</v>
+        <v>16.60545</v>
       </c>
       <c r="D7" t="n">
-        <v>15.9514</v>
+        <v>15.46493</v>
       </c>
       <c r="E7" t="n">
-        <v>16.27678</v>
+        <v>15.99931</v>
       </c>
       <c r="F7" t="n">
-        <v>22.04289</v>
+        <v>21.90992</v>
       </c>
       <c r="G7" t="n">
-        <v>33.63217</v>
+        <v>34.54044</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.93206</v>
+        <v>16.61055</v>
       </c>
       <c r="D8" t="n">
-        <v>16.05426</v>
+        <v>15.83118</v>
       </c>
       <c r="E8" t="n">
-        <v>16.42037</v>
+        <v>16.1223</v>
       </c>
       <c r="F8" t="n">
-        <v>21.37359</v>
+        <v>22.05207</v>
       </c>
       <c r="G8" t="n">
-        <v>34.26305</v>
+        <v>34.60617</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.60968</v>
+        <v>0.61455</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1329</v>
+        <v>1.09923</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60514</v>
+        <v>0.60773</v>
       </c>
       <c r="D11" t="n">
-        <v>1.10239</v>
+        <v>1.138</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.595</v>
+        <v>0.6045199999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.10781</v>
+        <v>1.11145</v>
       </c>
     </row>
   </sheetData>
